--- a/sample_data/raw_data_blank.xlsx
+++ b/sample_data/raw_data_blank.xlsx
@@ -514,7 +514,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Leave level 4 (normal) out. YYYY alone = month unknown (counted as July). ? = reached by the latest month.</t>
+          <t xml:space="preserve">  Leave level 4 (normal) out. YYYY alone = month unknown (counted as July). ? = reached by the latest month (the patient has reached this level, but we don’t know the month).</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       <formula1>"TH,EN"</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C2000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" prompt="MM/YYYY in AD, e.g. 03/2026"/>
-    <dataValidation sqref="E2:AZ2000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" prompt="Month the patient first reached this level: MM/YYYY, YYYY if only the year is known, or ? (reached by the latest month). Blank = not reached."/>
+    <dataValidation sqref="E2:AZ2000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" prompt="Month the patient first reached this level: MM/YYYY, YYYY if only the year is known, or ? (reached by the latest month (the patient has reached this level, but we don’t know the month)). Blank = not reached."/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
